--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-related-person.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T06:17:07+00:00</t>
+    <t>2026-10-16T08:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
